--- a/VALORIZADO TOBERIN.xlsx
+++ b/VALORIZADO TOBERIN.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
   <si>
     <t>Categoría</t>
   </si>
@@ -52,72 +52,27 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Categoría producto importación</t>
-  </si>
-  <si>
     <t>Categoría producto</t>
   </si>
   <si>
-    <t>229798-01</t>
+    <t>BA403008</t>
   </si>
   <si>
     <t>4515/C/X/WI 700</t>
   </si>
   <si>
-    <t>4515/C/X/WI 557</t>
-  </si>
-  <si>
-    <t>4707/WI700</t>
-  </si>
-  <si>
-    <t>4707/X/WI700</t>
-  </si>
-  <si>
-    <t>4707/WI557</t>
-  </si>
-  <si>
-    <t>4707/X/WI557</t>
-  </si>
-  <si>
-    <t>4709/WI700</t>
-  </si>
-  <si>
-    <t>4709/X/WI700</t>
-  </si>
-  <si>
-    <t>BOSTROM</t>
+    <t>DANA</t>
   </si>
   <si>
     <t>FRAS-LE</t>
   </si>
   <si>
-    <t>BOLSA DE AIRE LUMBAR CAMARA SIMPLE</t>
+    <t>KIT SPLINDER AGRALE 170MM x 33MM</t>
   </si>
   <si>
     <t>BLOQUE TRASERA Y TRAILER (1 JG VIENE X 8 BLOQUES) PARA MACK  R600 -R700/CHEVOLET SUPER BRIGARDIER, KODIAK/ BRIGADIER / DODGE 600 f /INTERNATIONAL 4300-HI-HI500 / FORD F800,FT9000 FREIGHTLINER/MACK/ROMARCO TRAILER  (solo si la zapata tiene 7 pulgadas de ancho)/DITE TRAILER/INCA FRUEHAUE TRAILER</t>
   </si>
   <si>
-    <t>BLOQUE TRASERA Y TRAILER PARA (1 JG VIENE X 8 BLOQUES) PARA MACK  R600 -R700/CHEVOLET SUPER BRIGARDIER, KODIAK/ BRIGADIER / DODGE 600 f /INTERNATIONAL 4300-HI-HI500 / FORD F800,FT9000 FREIGHTLINER/MACK/ROMARCO TRAILER (solo si la zapata tiene 7 pulgadas de ancho)/DITE TRAILER/INCA FRUEHAUE TRAILER</t>
-  </si>
-  <si>
-    <t>BLOQUE TRASERO  (1 JG VIENE X 8 BLOQUES) PARA KENWORTH T300-T800/MACK CT713INTERNATIONAL 4700 -4300-7600/ ROCKWELL AXLE / FREIGHTLINER M2 106-112</t>
-  </si>
-  <si>
-    <t>BLOQUE TRASERA (1 JG VIENE X 8 BLOQUES) PARA KENWORTH T300-T800/MACK CT713INTERNATIONAL 4700 -4300-7600/ ROCKWELL AXLE / FREIGHTLINER M2 106-113</t>
-  </si>
-  <si>
-    <t>BLOQUE TRASERA (1 JG VIENE X 8 BLOQUES) PARA KENWORTH T300-T800/MACK CT713INTERNATIONAL 4700 -4300-7600/ ROCKWELL AXLE / FREIGHTLINER M2 106-112</t>
-  </si>
-  <si>
-    <t>BLOQUE TRASERA (1 JG VIENE X 8 BLOQUES) PARA INTERNATIONAL 9400--9900/EATON BRAKES 16.5" DIA. X 7" /MERCEDES CAMION CLASE7 / KENWORTH T600,T800 EJE EATON MODELO 2002-2007-CAMION 7600 INTER</t>
-  </si>
-  <si>
-    <t>BLOQUE TRASERA (1 JG VIENE X 8 BLOQUES) PARA INTERNATIONAL 9400--9900/EATON BRAKES 16.5" DIA. X 7" /MERCEDES CAMION CLASE7 / KENWORTH T600,T800 EJE EATON MODELO 2002-2007-CAMION 7600 INTER.</t>
-  </si>
-  <si>
-    <t>NACIONAL</t>
-  </si>
-  <si>
     <t>Unidad</t>
   </si>
   <si>
@@ -136,13 +91,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 30/09/2025 09:57:11</t>
+    <t>Período: 31/10/2025 09:15:37</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 08/09/2025 09:57:26</t>
+    <t>Fecha y hora de generación: 21/10/2025 09:15:53</t>
   </si>
 </sst>
 </file>
@@ -556,28 +511,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -593,7 +548,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="3" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -609,12 +564,12 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="4" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="I7" s="5" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -663,287 +618,63 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E10" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="I10" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J10">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K10">
-        <v>29533.99</v>
+        <v>1092835.17</v>
       </c>
       <c r="L10">
-        <v>295339.9</v>
+        <v>1092835.17</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11">
         <v>24</v>
       </c>
-      <c r="D11" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I11" t="s">
-        <v>34</v>
-      </c>
-      <c r="J11">
-        <v>224</v>
-      </c>
       <c r="K11">
-        <v>105790.34</v>
+        <v>105339.15</v>
       </c>
       <c r="L11">
-        <v>23697036.16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I12" t="s">
-        <v>34</v>
-      </c>
-      <c r="J12">
-        <v>6</v>
-      </c>
-      <c r="K12">
-        <v>123453.61</v>
-      </c>
-      <c r="L12">
-        <v>740721.66</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F13" t="s">
-        <v>24</v>
-      </c>
-      <c r="I13" t="s">
-        <v>34</v>
-      </c>
-      <c r="J13">
-        <v>80</v>
-      </c>
-      <c r="K13">
-        <v>114350.05</v>
-      </c>
-      <c r="L13">
-        <v>9148004</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" t="s">
-        <v>29</v>
-      </c>
-      <c r="E14" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" t="s">
-        <v>24</v>
-      </c>
-      <c r="I14" t="s">
-        <v>34</v>
-      </c>
-      <c r="J14">
-        <v>100</v>
-      </c>
-      <c r="K14">
-        <v>117970</v>
-      </c>
-      <c r="L14">
-        <v>11797000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E15" t="s">
-        <v>24</v>
-      </c>
-      <c r="F15" t="s">
-        <v>24</v>
-      </c>
-      <c r="I15" t="s">
-        <v>34</v>
-      </c>
-      <c r="J15">
-        <v>15</v>
-      </c>
-      <c r="K15">
-        <v>124750.75</v>
-      </c>
-      <c r="L15">
-        <v>1871261.25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" t="s">
-        <v>29</v>
-      </c>
-      <c r="E16" t="s">
-        <v>24</v>
-      </c>
-      <c r="F16" t="s">
-        <v>24</v>
-      </c>
-      <c r="I16" t="s">
-        <v>34</v>
-      </c>
-      <c r="J16">
-        <v>20</v>
-      </c>
-      <c r="K16">
-        <v>132916.65</v>
-      </c>
-      <c r="L16">
-        <v>2658333</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
-      <c r="A17" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E17" t="s">
-        <v>24</v>
-      </c>
-      <c r="F17" t="s">
-        <v>24</v>
-      </c>
-      <c r="I17" t="s">
-        <v>34</v>
-      </c>
-      <c r="J17">
-        <v>70</v>
-      </c>
-      <c r="K17">
-        <v>116710.59</v>
-      </c>
-      <c r="L17">
-        <v>8169741.3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
-      <c r="A18" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" t="s">
-        <v>32</v>
-      </c>
-      <c r="E18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F18" t="s">
-        <v>24</v>
-      </c>
-      <c r="I18" t="s">
-        <v>34</v>
-      </c>
-      <c r="J18">
-        <v>30</v>
-      </c>
-      <c r="K18">
-        <v>123480</v>
-      </c>
-      <c r="L18">
-        <v>3704400</v>
+        <v>2528139.6</v>
       </c>
     </row>
   </sheetData>

--- a/VALORIZADO TOBERIN.xlsx
+++ b/VALORIZADO TOBERIN.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="32">
   <si>
     <t>Categoría</t>
   </si>
@@ -55,21 +55,33 @@
     <t>Categoría producto</t>
   </si>
   <si>
+    <t>Categoría producto importación</t>
+  </si>
+  <si>
     <t>BA403008</t>
   </si>
   <si>
+    <t>WAB9650011030</t>
+  </si>
+  <si>
     <t>4515/C/X/WI 700</t>
   </si>
   <si>
     <t>DANA</t>
   </si>
   <si>
+    <t>WABCO</t>
+  </si>
+  <si>
     <t>FRAS-LE</t>
   </si>
   <si>
     <t>KIT SPLINDER AGRALE 170MM x 33MM</t>
   </si>
   <si>
+    <t>PEDAL CLUTCH M2-106  M2-112 COLUMBIA CARRERA O DESPLAZAMIENTO 194 MM</t>
+  </si>
+  <si>
     <t>BLOQUE TRASERA Y TRAILER (1 JG VIENE X 8 BLOQUES) PARA MACK  R600 -R700/CHEVOLET SUPER BRIGARDIER, KODIAK/ BRIGADIER / DODGE 600 f /INTERNATIONAL 4300-HI-HI500 / FORD F800,FT9000 FREIGHTLINER/MACK/ROMARCO TRAILER  (solo si la zapata tiene 7 pulgadas de ancho)/DITE TRAILER/INCA FRUEHAUE TRAILER</t>
   </si>
   <si>
@@ -91,13 +103,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 31/10/2025 09:44:16</t>
+    <t>Período: 31/10/2025 12:37:31</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 23/10/2025 09:45:06</t>
+    <t>Fecha y hora de generación: 27/10/2025 12:37:44</t>
   </si>
 </sst>
 </file>
@@ -511,28 +523,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -548,7 +560,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -564,12 +576,12 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="I7" s="5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -618,22 +630,22 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" t="s">
         <v>17</v>
       </c>
-      <c r="E10" t="s">
-        <v>15</v>
-      </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I10" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -647,33 +659,65 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11">
+        <v>59</v>
+      </c>
+      <c r="K11">
+        <v>1268236.6</v>
+      </c>
+      <c r="L11">
+        <v>74825959.40000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="B11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B12" t="s">
         <v>16</v>
       </c>
-      <c r="D11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="C12" t="s">
         <v>19</v>
       </c>
-      <c r="J11">
+      <c r="D12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12">
         <v>24</v>
       </c>
-      <c r="K11">
+      <c r="K12">
         <v>105339.15</v>
       </c>
-      <c r="L11">
+      <c r="L12">
         <v>2528139.6</v>
       </c>
     </row>

--- a/VALORIZADO TOBERIN.xlsx
+++ b/VALORIZADO TOBERIN.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="54">
   <si>
     <t>Categoría</t>
   </si>
@@ -67,6 +67,39 @@
     <t>4515/C/X/WI 700</t>
   </si>
   <si>
+    <t>4515/C/WI 557</t>
+  </si>
+  <si>
+    <t>4707/WI700</t>
+  </si>
+  <si>
+    <t>4707/X/WI700</t>
+  </si>
+  <si>
+    <t>4707/WI557</t>
+  </si>
+  <si>
+    <t>4709/WI700</t>
+  </si>
+  <si>
+    <t>4720/WI700</t>
+  </si>
+  <si>
+    <t>4715/WI700</t>
+  </si>
+  <si>
+    <t>4709/X/WI557</t>
+  </si>
+  <si>
+    <t>CA/32/X/WI557</t>
+  </si>
+  <si>
+    <t>700078C-01-E</t>
+  </si>
+  <si>
+    <t>4715/X/WI700</t>
+  </si>
+  <si>
     <t>DANA</t>
   </si>
   <si>
@@ -85,6 +118,39 @@
     <t>BLOQUE TRASERA Y TRAILER (1 JG VIENE X 8 BLOQUES) PARA MACK  R600 -R700/CHEVOLET SUPER BRIGARDIER, KODIAK/ BRIGADIER / DODGE 600 f /INTERNATIONAL 4300-HI-HI500 / FORD F800,FT9000 FREIGHTLINER/MACK/ROMARCO TRAILER  (solo si la zapata tiene 7 pulgadas de ancho)/DITE TRAILER/INCA FRUEHAUE TRAILER</t>
   </si>
   <si>
+    <t>BLOQUE TRASERA Y TRAILER (1 JG VIENE X 8 BLOQUES) PARA MACK  R600 -R700/CHEVOLET SUPER BRIGARDIER, KODIAK/ BRIGADIER / DODGE 600 f /INTERNATIONAL 4300-HI-HI500 / FORD F800,FT9000 FREIGHTLINER/MACK/ROMARCO TRAILER (solo si la zapata tiene 7 pulgadas de ancho)/DITE TRAILER/INCA FRUEHAUE TRAILER</t>
+  </si>
+  <si>
+    <t>BLOQUE TRASERO  (1 JG VIENE X 8 BLOQUES) PARA KENWORTH T300-T800/MACK CT713INTERNATIONAL 4700 -4300-7600/ ROCKWELL AXLE / FREIGHTLINER M2 106-112</t>
+  </si>
+  <si>
+    <t>BLOQUE TRASERA (1 JG VIENE X 8 BLOQUES) PARA KENWORTH T300-T800/MACK CT713INTERNATIONAL 4700 -4300-7600/ ROCKWELL AXLE / FREIGHTLINER M2 106-113</t>
+  </si>
+  <si>
+    <t>BLOQUE TRASERA (1 JG VIENE X 8 BLOQUES) PARA KENWORTH T300-T800/MACK CT713INTERNATIONAL 4700 -4300-7600/ ROCKWELL AXLE / FREIGHTLINER M2 106-112</t>
+  </si>
+  <si>
+    <t>BLOQUE TRASERA (1 JG VIENE X 8 BLOQUES) PARA INTERNATIONAL 9400--9900/EATON BRAKES 16.5" DIA. X 7" /MERCEDES CAMION CLASE7 / KENWORTH T600,T800 EJE EATON MODELO 2002-2007-CAMION 7600 INTER</t>
+  </si>
+  <si>
+    <t>BLOQUE DELANTERO (1 JG VIENE X 8 BLOQUES) PARA FREIGHTLINER  COLUMBIA-M2 106 -112 -CASCADIA/INTERNATIONAL  7600-4300-PROSTAR/ KENWORTH T800, MERITOR TAMBOR DIA 16,5" X ANCHO 5"/ COMPAÑERO CON EL 4707</t>
+  </si>
+  <si>
+    <t>BLOQUE DELANTERO (1 JG VIENE X 8 BLOQUES) PARA FORD F-800/INTERNATIONAL 4700, 9400 TAMBOR DIA 16.5" X 6 " ANCHO /EJE ROCKWELL./BLUE BIRD./FRENO DELANTERO BOLQUETA INTERNATIONAL 7600</t>
+  </si>
+  <si>
+    <t>BLOQUE TRASERA CON SOBRE MEDIDA PARA INTERNATIONAL 9400--9900/EATON BRAKES 16.5" DIA. X 7" /MERCEDES CAMION CLASE7 / KENWORTH T600,T800 EJE EATON MODELO 2002-2007-CAMION 7600 INTER./1 JUEGO TIENE 8 BLOQUES; (KENWORTH T800 PARA EJE MARCA DANA) VENTA MINIMA 1 CAJA QUE TRAE 2 JUEGOS (16 BLOQUES) EL PRECIO DE LISTA ES POR 1 JUEGO</t>
+  </si>
+  <si>
+    <t>BLOQUE TRAILER (CON SOBRE MEDIDA .86 MILESIMAS DE PULGADA MAS GRUESO) PARA ROMARCO CAMPANA DIAM "16.5 x 8" ANCHO</t>
+  </si>
+  <si>
+    <t>REMACHE ACERADO 10-8 SEMI TUBULAR PARA BANDA PERFORADA (PAQUETE POR MILLAR)</t>
+  </si>
+  <si>
+    <t>BLOQUE DELANTERO(CON SOBRE MEDIDA .86 MILESIMAS DE PULGADA MAS GRUESO) PARA INTERNATIONAL WORKSTAR, 4700, 9400  FORD F-800/TAMBOR DIA 16.5" X 6 " ANCHO /EJE ROCKWELL./BLUE BIRD./FRENO DELANTERO VOLQUETA INTERNATIONAL 7600</t>
+  </si>
+  <si>
     <t>Unidad</t>
   </si>
   <si>
@@ -103,13 +169,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 31/10/2025 12:37:31</t>
+    <t>Período: 31/10/2025 08:45:56</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 27/10/2025 12:37:44</t>
+    <t>Fecha y hora de generación: 30/10/2025 08:46:40</t>
   </si>
 </sst>
 </file>
@@ -523,28 +589,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -560,7 +626,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="3" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -576,12 +642,12 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="4" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="I7" s="5" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -633,19 +699,19 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F10" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="I10" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -665,19 +731,19 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F11" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="I11" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="J11">
         <v>59</v>
@@ -697,28 +763,380 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J12">
+        <v>354</v>
+      </c>
+      <c r="K12">
+        <v>103344.83</v>
+      </c>
+      <c r="L12">
+        <v>36584069.82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" t="s">
+        <v>45</v>
+      </c>
+      <c r="J13">
+        <v>24</v>
+      </c>
+      <c r="K13">
+        <v>117534.05</v>
+      </c>
+      <c r="L13">
+        <v>2820817.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" t="s">
+        <v>45</v>
+      </c>
+      <c r="J14">
+        <v>60</v>
+      </c>
+      <c r="K14">
+        <v>113167.54</v>
+      </c>
+      <c r="L14">
+        <v>6790052.4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
         <v>19</v>
       </c>
-      <c r="D12" t="s">
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" t="s">
+        <v>45</v>
+      </c>
+      <c r="J15">
+        <v>15</v>
+      </c>
+      <c r="K15">
+        <v>118404.06</v>
+      </c>
+      <c r="L15">
+        <v>1776060.9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" t="s">
+        <v>45</v>
+      </c>
+      <c r="J16">
+        <v>60</v>
+      </c>
+      <c r="K16">
+        <v>124047</v>
+      </c>
+      <c r="L16">
+        <v>7442820</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" t="s">
+        <v>45</v>
+      </c>
+      <c r="J17">
+        <v>180</v>
+      </c>
+      <c r="K17">
+        <v>113701.69</v>
+      </c>
+      <c r="L17">
+        <v>20466304.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
         <v>22</v>
       </c>
-      <c r="E12" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" t="s">
-        <v>19</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="C18" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" t="s">
+        <v>30</v>
+      </c>
+      <c r="F18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" t="s">
+        <v>45</v>
+      </c>
+      <c r="J18">
+        <v>32</v>
+      </c>
+      <c r="K18">
+        <v>81253.13</v>
+      </c>
+      <c r="L18">
+        <v>2600100.16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" t="s">
         <v>23</v>
       </c>
-      <c r="J12">
+      <c r="C19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" t="s">
+        <v>45</v>
+      </c>
+      <c r="J19">
+        <v>6</v>
+      </c>
+      <c r="K19">
+        <v>98376.67</v>
+      </c>
+      <c r="L19">
+        <v>590260.02</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
         <v>24</v>
       </c>
-      <c r="K12">
-        <v>105339.15</v>
-      </c>
-      <c r="L12">
-        <v>2528139.6</v>
+      <c r="C20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" t="s">
+        <v>30</v>
+      </c>
+      <c r="F20" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" t="s">
+        <v>45</v>
+      </c>
+      <c r="J20">
+        <v>4</v>
+      </c>
+      <c r="K20">
+        <v>159095</v>
+      </c>
+      <c r="L20">
+        <v>636380</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21" t="s">
+        <v>30</v>
+      </c>
+      <c r="F21" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" t="s">
+        <v>45</v>
+      </c>
+      <c r="J21">
+        <v>50</v>
+      </c>
+      <c r="K21">
+        <v>132600</v>
+      </c>
+      <c r="L21">
+        <v>6630000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" t="s">
+        <v>30</v>
+      </c>
+      <c r="I22" t="s">
+        <v>45</v>
+      </c>
+      <c r="J22">
+        <v>18</v>
+      </c>
+      <c r="K22">
+        <v>120464.5</v>
+      </c>
+      <c r="L22">
+        <v>2168361</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" t="s">
+        <v>30</v>
+      </c>
+      <c r="F23" t="s">
+        <v>30</v>
+      </c>
+      <c r="I23" t="s">
+        <v>45</v>
+      </c>
+      <c r="J23">
+        <v>12</v>
+      </c>
+      <c r="K23">
+        <v>125228</v>
+      </c>
+      <c r="L23">
+        <v>1502736</v>
       </c>
     </row>
   </sheetData>

--- a/VALORIZADO TOBERIN.xlsx
+++ b/VALORIZADO TOBERIN.xlsx
@@ -169,13 +169,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 31/10/2025 08:45:56</t>
+    <t>Período: 30/11/2025 12:29:18</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 30/10/2025 08:46:40</t>
+    <t>Fecha y hora de generación: 01/11/2025 12:29:40</t>
   </si>
 </sst>
 </file>

--- a/VALORIZADO TOBERIN.xlsx
+++ b/VALORIZADO TOBERIN.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="32">
   <si>
     <t>Categoría</t>
   </si>
@@ -67,39 +67,6 @@
     <t>4515/C/X/WI 700</t>
   </si>
   <si>
-    <t>4515/C/WI 557</t>
-  </si>
-  <si>
-    <t>4707/WI700</t>
-  </si>
-  <si>
-    <t>4707/X/WI700</t>
-  </si>
-  <si>
-    <t>4707/WI557</t>
-  </si>
-  <si>
-    <t>4709/WI700</t>
-  </si>
-  <si>
-    <t>4720/WI700</t>
-  </si>
-  <si>
-    <t>4715/WI700</t>
-  </si>
-  <si>
-    <t>4709/X/WI557</t>
-  </si>
-  <si>
-    <t>CA/32/X/WI557</t>
-  </si>
-  <si>
-    <t>700078C-01-E</t>
-  </si>
-  <si>
-    <t>4715/X/WI700</t>
-  </si>
-  <si>
     <t>DANA</t>
   </si>
   <si>
@@ -118,39 +85,6 @@
     <t>BLOQUE TRASERA Y TRAILER (1 JG VIENE X 8 BLOQUES) PARA MACK  R600 -R700/CHEVOLET SUPER BRIGARDIER, KODIAK/ BRIGADIER / DODGE 600 f /INTERNATIONAL 4300-HI-HI500 / FORD F800,FT9000 FREIGHTLINER/MACK/ROMARCO TRAILER  (solo si la zapata tiene 7 pulgadas de ancho)/DITE TRAILER/INCA FRUEHAUE TRAILER</t>
   </si>
   <si>
-    <t>BLOQUE TRASERA Y TRAILER (1 JG VIENE X 8 BLOQUES) PARA MACK  R600 -R700/CHEVOLET SUPER BRIGARDIER, KODIAK/ BRIGADIER / DODGE 600 f /INTERNATIONAL 4300-HI-HI500 / FORD F800,FT9000 FREIGHTLINER/MACK/ROMARCO TRAILER (solo si la zapata tiene 7 pulgadas de ancho)/DITE TRAILER/INCA FRUEHAUE TRAILER</t>
-  </si>
-  <si>
-    <t>BLOQUE TRASERO  (1 JG VIENE X 8 BLOQUES) PARA KENWORTH T300-T800/MACK CT713INTERNATIONAL 4700 -4300-7600/ ROCKWELL AXLE / FREIGHTLINER M2 106-112</t>
-  </si>
-  <si>
-    <t>BLOQUE TRASERA (1 JG VIENE X 8 BLOQUES) PARA KENWORTH T300-T800/MACK CT713INTERNATIONAL 4700 -4300-7600/ ROCKWELL AXLE / FREIGHTLINER M2 106-113</t>
-  </si>
-  <si>
-    <t>BLOQUE TRASERA (1 JG VIENE X 8 BLOQUES) PARA KENWORTH T300-T800/MACK CT713INTERNATIONAL 4700 -4300-7600/ ROCKWELL AXLE / FREIGHTLINER M2 106-112</t>
-  </si>
-  <si>
-    <t>BLOQUE TRASERA (1 JG VIENE X 8 BLOQUES) PARA INTERNATIONAL 9400--9900/EATON BRAKES 16.5" DIA. X 7" /MERCEDES CAMION CLASE7 / KENWORTH T600,T800 EJE EATON MODELO 2002-2007-CAMION 7600 INTER</t>
-  </si>
-  <si>
-    <t>BLOQUE DELANTERO (1 JG VIENE X 8 BLOQUES) PARA FREIGHTLINER  COLUMBIA-M2 106 -112 -CASCADIA/INTERNATIONAL  7600-4300-PROSTAR/ KENWORTH T800, MERITOR TAMBOR DIA 16,5" X ANCHO 5"/ COMPAÑERO CON EL 4707</t>
-  </si>
-  <si>
-    <t>BLOQUE DELANTERO (1 JG VIENE X 8 BLOQUES) PARA FORD F-800/INTERNATIONAL 4700, 9400 TAMBOR DIA 16.5" X 6 " ANCHO /EJE ROCKWELL./BLUE BIRD./FRENO DELANTERO BOLQUETA INTERNATIONAL 7600</t>
-  </si>
-  <si>
-    <t>BLOQUE TRASERA CON SOBRE MEDIDA PARA INTERNATIONAL 9400--9900/EATON BRAKES 16.5" DIA. X 7" /MERCEDES CAMION CLASE7 / KENWORTH T600,T800 EJE EATON MODELO 2002-2007-CAMION 7600 INTER./1 JUEGO TIENE 8 BLOQUES; (KENWORTH T800 PARA EJE MARCA DANA) VENTA MINIMA 1 CAJA QUE TRAE 2 JUEGOS (16 BLOQUES) EL PRECIO DE LISTA ES POR 1 JUEGO</t>
-  </si>
-  <si>
-    <t>BLOQUE TRAILER (CON SOBRE MEDIDA .86 MILESIMAS DE PULGADA MAS GRUESO) PARA ROMARCO CAMPANA DIAM "16.5 x 8" ANCHO</t>
-  </si>
-  <si>
-    <t>REMACHE ACERADO 10-8 SEMI TUBULAR PARA BANDA PERFORADA (PAQUETE POR MILLAR)</t>
-  </si>
-  <si>
-    <t>BLOQUE DELANTERO(CON SOBRE MEDIDA .86 MILESIMAS DE PULGADA MAS GRUESO) PARA INTERNATIONAL WORKSTAR, 4700, 9400  FORD F-800/TAMBOR DIA 16.5" X 6 " ANCHO /EJE ROCKWELL./BLUE BIRD./FRENO DELANTERO VOLQUETA INTERNATIONAL 7600</t>
-  </si>
-  <si>
     <t>Unidad</t>
   </si>
   <si>
@@ -169,13 +103,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 30/11/2025 12:29:18</t>
+    <t>Período: 29/11/2025 22:19:30</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 01/11/2025 12:29:40</t>
+    <t>Fecha y hora de generación: 04/11/2025 22:19:49</t>
   </si>
 </sst>
 </file>
@@ -589,28 +523,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -626,7 +560,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="3" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -642,12 +576,12 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="4" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="I7" s="5" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -699,19 +633,19 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="E10" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I10" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -731,19 +665,19 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F11" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I11" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="J11">
         <v>59</v>
@@ -763,380 +697,28 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E12" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I12" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="J12">
-        <v>354</v>
+        <v>24</v>
       </c>
       <c r="K12">
         <v>103344.83</v>
       </c>
       <c r="L12">
-        <v>36584069.82</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" t="s">
-        <v>45</v>
-      </c>
-      <c r="J13">
-        <v>24</v>
-      </c>
-      <c r="K13">
-        <v>117534.05</v>
-      </c>
-      <c r="L13">
-        <v>2820817.2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" t="s">
-        <v>45</v>
-      </c>
-      <c r="J14">
-        <v>60</v>
-      </c>
-      <c r="K14">
-        <v>113167.54</v>
-      </c>
-      <c r="L14">
-        <v>6790052.4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" t="s">
-        <v>30</v>
-      </c>
-      <c r="F15" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" t="s">
-        <v>45</v>
-      </c>
-      <c r="J15">
-        <v>15</v>
-      </c>
-      <c r="K15">
-        <v>118404.06</v>
-      </c>
-      <c r="L15">
-        <v>1776060.9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" t="s">
-        <v>37</v>
-      </c>
-      <c r="E16" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" t="s">
-        <v>30</v>
-      </c>
-      <c r="I16" t="s">
-        <v>45</v>
-      </c>
-      <c r="J16">
-        <v>60</v>
-      </c>
-      <c r="K16">
-        <v>124047</v>
-      </c>
-      <c r="L16">
-        <v>7442820</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
-      <c r="A17" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" t="s">
-        <v>38</v>
-      </c>
-      <c r="E17" t="s">
-        <v>30</v>
-      </c>
-      <c r="F17" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" t="s">
-        <v>45</v>
-      </c>
-      <c r="J17">
-        <v>180</v>
-      </c>
-      <c r="K17">
-        <v>113701.69</v>
-      </c>
-      <c r="L17">
-        <v>20466304.2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
-      <c r="A18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" t="s">
-        <v>39</v>
-      </c>
-      <c r="E18" t="s">
-        <v>30</v>
-      </c>
-      <c r="F18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I18" t="s">
-        <v>45</v>
-      </c>
-      <c r="J18">
-        <v>32</v>
-      </c>
-      <c r="K18">
-        <v>81253.13</v>
-      </c>
-      <c r="L18">
-        <v>2600100.16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
-      <c r="A19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" t="s">
-        <v>40</v>
-      </c>
-      <c r="E19" t="s">
-        <v>30</v>
-      </c>
-      <c r="F19" t="s">
-        <v>30</v>
-      </c>
-      <c r="I19" t="s">
-        <v>45</v>
-      </c>
-      <c r="J19">
-        <v>6</v>
-      </c>
-      <c r="K19">
-        <v>98376.67</v>
-      </c>
-      <c r="L19">
-        <v>590260.02</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
-      <c r="A20" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" t="s">
-        <v>41</v>
-      </c>
-      <c r="E20" t="s">
-        <v>30</v>
-      </c>
-      <c r="F20" t="s">
-        <v>30</v>
-      </c>
-      <c r="I20" t="s">
-        <v>45</v>
-      </c>
-      <c r="J20">
-        <v>4</v>
-      </c>
-      <c r="K20">
-        <v>159095</v>
-      </c>
-      <c r="L20">
-        <v>636380</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
-      <c r="A21" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" t="s">
-        <v>42</v>
-      </c>
-      <c r="E21" t="s">
-        <v>30</v>
-      </c>
-      <c r="F21" t="s">
-        <v>30</v>
-      </c>
-      <c r="I21" t="s">
-        <v>45</v>
-      </c>
-      <c r="J21">
-        <v>50</v>
-      </c>
-      <c r="K21">
-        <v>132600</v>
-      </c>
-      <c r="L21">
-        <v>6630000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
-      <c r="A22" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" t="s">
-        <v>43</v>
-      </c>
-      <c r="E22" t="s">
-        <v>30</v>
-      </c>
-      <c r="F22" t="s">
-        <v>30</v>
-      </c>
-      <c r="I22" t="s">
-        <v>45</v>
-      </c>
-      <c r="J22">
-        <v>18</v>
-      </c>
-      <c r="K22">
-        <v>120464.5</v>
-      </c>
-      <c r="L22">
-        <v>2168361</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="A23" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" t="s">
-        <v>44</v>
-      </c>
-      <c r="E23" t="s">
-        <v>30</v>
-      </c>
-      <c r="F23" t="s">
-        <v>30</v>
-      </c>
-      <c r="I23" t="s">
-        <v>45</v>
-      </c>
-      <c r="J23">
-        <v>12</v>
-      </c>
-      <c r="K23">
-        <v>125228</v>
-      </c>
-      <c r="L23">
-        <v>1502736</v>
+        <v>2480275.92</v>
       </c>
     </row>
   </sheetData>

--- a/VALORIZADO TOBERIN.xlsx
+++ b/VALORIZADO TOBERIN.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
   <si>
     <t>Categoría</t>
   </si>
@@ -64,93 +64,18 @@
     <t>WAB9650011030</t>
   </si>
   <si>
-    <t>4515/C/X/WI 700</t>
-  </si>
-  <si>
-    <t>4515/C/WI 557</t>
-  </si>
-  <si>
-    <t>4707/WI700</t>
-  </si>
-  <si>
-    <t>4707/X/WI700</t>
-  </si>
-  <si>
-    <t>4707/WI557</t>
-  </si>
-  <si>
-    <t>4709/WI700</t>
-  </si>
-  <si>
-    <t>4720/WI700</t>
-  </si>
-  <si>
-    <t>4715/WI700</t>
-  </si>
-  <si>
-    <t>4709/X/WI557</t>
-  </si>
-  <si>
-    <t>CA/32/X/WI557</t>
-  </si>
-  <si>
-    <t>700078C-01-E</t>
-  </si>
-  <si>
-    <t>4715/X/WI700</t>
-  </si>
-  <si>
     <t>DANA</t>
   </si>
   <si>
     <t>WABCO</t>
   </si>
   <si>
-    <t>FRAS-LE</t>
-  </si>
-  <si>
     <t>KIT SPLINDER AGRALE 170MM x 33MM</t>
   </si>
   <si>
     <t>PEDAL CLUTCH M2-106  M2-112 COLUMBIA CARRERA O DESPLAZAMIENTO 194 MM</t>
   </si>
   <si>
-    <t>BLOQUE TRASERA Y TRAILER (1 JG VIENE X 8 BLOQUES) PARA MACK  R600 -R700/CHEVOLET SUPER BRIGARDIER, KODIAK/ BRIGADIER / DODGE 600 f /INTERNATIONAL 4300-HI-HI500 / FORD F800,FT9000 FREIGHTLINER/MACK/ROMARCO TRAILER  (solo si la zapata tiene 7 pulgadas de ancho)/DITE TRAILER/INCA FRUEHAUE TRAILER</t>
-  </si>
-  <si>
-    <t>BLOQUE TRASERA Y TRAILER (1 JG VIENE X 8 BLOQUES) PARA MACK  R600 -R700/CHEVOLET SUPER BRIGARDIER, KODIAK/ BRIGADIER / DODGE 600 f /INTERNATIONAL 4300-HI-HI500 / FORD F800,FT9000 FREIGHTLINER/MACK/ROMARCO TRAILER (solo si la zapata tiene 7 pulgadas de ancho)/DITE TRAILER/INCA FRUEHAUE TRAILER</t>
-  </si>
-  <si>
-    <t>BLOQUE TRASERO  (1 JG VIENE X 8 BLOQUES) PARA KENWORTH T300-T800/MACK CT713INTERNATIONAL 4700 -4300-7600/ ROCKWELL AXLE / FREIGHTLINER M2 106-112</t>
-  </si>
-  <si>
-    <t>BLOQUE TRASERA (1 JG VIENE X 8 BLOQUES) PARA KENWORTH T300-T800/MACK CT713INTERNATIONAL 4700 -4300-7600/ ROCKWELL AXLE / FREIGHTLINER M2 106-113</t>
-  </si>
-  <si>
-    <t>BLOQUE TRASERA (1 JG VIENE X 8 BLOQUES) PARA KENWORTH T300-T800/MACK CT713INTERNATIONAL 4700 -4300-7600/ ROCKWELL AXLE / FREIGHTLINER M2 106-112</t>
-  </si>
-  <si>
-    <t>BLOQUE TRASERA (1 JG VIENE X 8 BLOQUES) PARA INTERNATIONAL 9400--9900/EATON BRAKES 16.5" DIA. X 7" /MERCEDES CAMION CLASE7 / KENWORTH T600,T800 EJE EATON MODELO 2002-2007-CAMION 7600 INTER</t>
-  </si>
-  <si>
-    <t>BLOQUE DELANTERO (1 JG VIENE X 8 BLOQUES) PARA FREIGHTLINER  COLUMBIA-M2 106 -112 -CASCADIA/INTERNATIONAL  7600-4300-PROSTAR/ KENWORTH T800, MERITOR TAMBOR DIA 16,5" X ANCHO 5"/ COMPAÑERO CON EL 4707</t>
-  </si>
-  <si>
-    <t>BLOQUE DELANTERO (1 JG VIENE X 8 BLOQUES) PARA FORD F-800/INTERNATIONAL 4700, 9400 TAMBOR DIA 16.5" X 6 " ANCHO /EJE ROCKWELL./BLUE BIRD./FRENO DELANTERO BOLQUETA INTERNATIONAL 7600</t>
-  </si>
-  <si>
-    <t>BLOQUE TRASERA CON SOBRE MEDIDA PARA INTERNATIONAL 9400--9900/EATON BRAKES 16.5" DIA. X 7" /MERCEDES CAMION CLASE7 / KENWORTH T600,T800 EJE EATON MODELO 2002-2007-CAMION 7600 INTER./1 JUEGO TIENE 8 BLOQUES; (KENWORTH T800 PARA EJE MARCA DANA) VENTA MINIMA 1 CAJA QUE TRAE 2 JUEGOS (16 BLOQUES) EL PRECIO DE LISTA ES POR 1 JUEGO</t>
-  </si>
-  <si>
-    <t>BLOQUE TRAILER (CON SOBRE MEDIDA .86 MILESIMAS DE PULGADA MAS GRUESO) PARA ROMARCO CAMPANA DIAM "16.5 x 8" ANCHO</t>
-  </si>
-  <si>
-    <t>REMACHE ACERADO 10-8 SEMI TUBULAR PARA BANDA PERFORADA (PAQUETE POR MILLAR)</t>
-  </si>
-  <si>
-    <t>BLOQUE DELANTERO(CON SOBRE MEDIDA .86 MILESIMAS DE PULGADA MAS GRUESO) PARA INTERNATIONAL WORKSTAR, 4700, 9400  FORD F-800/TAMBOR DIA 16.5" X 6 " ANCHO /EJE ROCKWELL./BLUE BIRD./FRENO DELANTERO VOLQUETA INTERNATIONAL 7600</t>
-  </si>
-  <si>
     <t>Unidad</t>
   </si>
   <si>
@@ -169,13 +94,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 31/10/2025 08:45:56</t>
+    <t>Período: 30/11/2025 08:47:22</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 30/10/2025 08:46:40</t>
+    <t>Fecha y hora de generación: 26/11/2025 08:48:16</t>
   </si>
 </sst>
 </file>
@@ -589,28 +514,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -626,7 +551,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="3" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -642,12 +567,12 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="4" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="I7" s="5" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -699,19 +624,19 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I10" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -731,412 +656,28 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="I11" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="J11">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K11">
         <v>1268236.6</v>
       </c>
       <c r="L11">
-        <v>74825959.40000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" t="s">
-        <v>33</v>
-      </c>
-      <c r="E12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" t="s">
-        <v>30</v>
-      </c>
-      <c r="I12" t="s">
-        <v>45</v>
-      </c>
-      <c r="J12">
-        <v>354</v>
-      </c>
-      <c r="K12">
-        <v>103344.83</v>
-      </c>
-      <c r="L12">
-        <v>36584069.82</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" t="s">
-        <v>45</v>
-      </c>
-      <c r="J13">
-        <v>24</v>
-      </c>
-      <c r="K13">
-        <v>117534.05</v>
-      </c>
-      <c r="L13">
-        <v>2820817.2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" t="s">
-        <v>45</v>
-      </c>
-      <c r="J14">
-        <v>60</v>
-      </c>
-      <c r="K14">
-        <v>113167.54</v>
-      </c>
-      <c r="L14">
-        <v>6790052.4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" t="s">
-        <v>30</v>
-      </c>
-      <c r="F15" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" t="s">
-        <v>45</v>
-      </c>
-      <c r="J15">
-        <v>15</v>
-      </c>
-      <c r="K15">
-        <v>118404.06</v>
-      </c>
-      <c r="L15">
-        <v>1776060.9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" t="s">
-        <v>37</v>
-      </c>
-      <c r="E16" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" t="s">
-        <v>30</v>
-      </c>
-      <c r="I16" t="s">
-        <v>45</v>
-      </c>
-      <c r="J16">
-        <v>60</v>
-      </c>
-      <c r="K16">
-        <v>124047</v>
-      </c>
-      <c r="L16">
-        <v>7442820</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
-      <c r="A17" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" t="s">
-        <v>38</v>
-      </c>
-      <c r="E17" t="s">
-        <v>30</v>
-      </c>
-      <c r="F17" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" t="s">
-        <v>45</v>
-      </c>
-      <c r="J17">
-        <v>180</v>
-      </c>
-      <c r="K17">
-        <v>113701.69</v>
-      </c>
-      <c r="L17">
-        <v>20466304.2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
-      <c r="A18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" t="s">
-        <v>39</v>
-      </c>
-      <c r="E18" t="s">
-        <v>30</v>
-      </c>
-      <c r="F18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I18" t="s">
-        <v>45</v>
-      </c>
-      <c r="J18">
-        <v>32</v>
-      </c>
-      <c r="K18">
-        <v>81253.13</v>
-      </c>
-      <c r="L18">
-        <v>2600100.16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
-      <c r="A19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" t="s">
-        <v>40</v>
-      </c>
-      <c r="E19" t="s">
-        <v>30</v>
-      </c>
-      <c r="F19" t="s">
-        <v>30</v>
-      </c>
-      <c r="I19" t="s">
-        <v>45</v>
-      </c>
-      <c r="J19">
-        <v>6</v>
-      </c>
-      <c r="K19">
-        <v>98376.67</v>
-      </c>
-      <c r="L19">
-        <v>590260.02</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
-      <c r="A20" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" t="s">
-        <v>41</v>
-      </c>
-      <c r="E20" t="s">
-        <v>30</v>
-      </c>
-      <c r="F20" t="s">
-        <v>30</v>
-      </c>
-      <c r="I20" t="s">
-        <v>45</v>
-      </c>
-      <c r="J20">
-        <v>4</v>
-      </c>
-      <c r="K20">
-        <v>159095</v>
-      </c>
-      <c r="L20">
-        <v>636380</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
-      <c r="A21" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" t="s">
-        <v>42</v>
-      </c>
-      <c r="E21" t="s">
-        <v>30</v>
-      </c>
-      <c r="F21" t="s">
-        <v>30</v>
-      </c>
-      <c r="I21" t="s">
-        <v>45</v>
-      </c>
-      <c r="J21">
-        <v>50</v>
-      </c>
-      <c r="K21">
-        <v>132600</v>
-      </c>
-      <c r="L21">
-        <v>6630000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
-      <c r="A22" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" t="s">
-        <v>43</v>
-      </c>
-      <c r="E22" t="s">
-        <v>30</v>
-      </c>
-      <c r="F22" t="s">
-        <v>30</v>
-      </c>
-      <c r="I22" t="s">
-        <v>45</v>
-      </c>
-      <c r="J22">
-        <v>18</v>
-      </c>
-      <c r="K22">
-        <v>120464.5</v>
-      </c>
-      <c r="L22">
-        <v>2168361</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="A23" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" t="s">
-        <v>44</v>
-      </c>
-      <c r="E23" t="s">
-        <v>30</v>
-      </c>
-      <c r="F23" t="s">
-        <v>30</v>
-      </c>
-      <c r="I23" t="s">
-        <v>45</v>
-      </c>
-      <c r="J23">
-        <v>12</v>
-      </c>
-      <c r="K23">
-        <v>125228</v>
-      </c>
-      <c r="L23">
-        <v>1502736</v>
+        <v>72289486.2</v>
       </c>
     </row>
   </sheetData>

--- a/VALORIZADO TOBERIN.xlsx
+++ b/VALORIZADO TOBERIN.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="61">
   <si>
     <t>Categoría</t>
   </si>
@@ -61,19 +61,115 @@
     <t>BA403008</t>
   </si>
   <si>
-    <t>WAB9650011030</t>
+    <t>4515/C/X/WI 700</t>
+  </si>
+  <si>
+    <t>4515/C/WI 700</t>
+  </si>
+  <si>
+    <t>4515/C/X/WI 557</t>
+  </si>
+  <si>
+    <t>4707/WI700</t>
+  </si>
+  <si>
+    <t>4707/WI557</t>
+  </si>
+  <si>
+    <t>4709/WI700</t>
+  </si>
+  <si>
+    <t>4720/WI700</t>
+  </si>
+  <si>
+    <t>4719/WI700</t>
+  </si>
+  <si>
+    <t>4715/WI700</t>
+  </si>
+  <si>
+    <t>FD/88/X/AF/700</t>
+  </si>
+  <si>
+    <t>4709/X/WI557</t>
+  </si>
+  <si>
+    <t>4709/WI557</t>
+  </si>
+  <si>
+    <t>4718/X/WI700</t>
+  </si>
+  <si>
+    <t>4719/WI557</t>
+  </si>
+  <si>
+    <t>MB/191_AF/700</t>
+  </si>
+  <si>
+    <t>MB/191/X/AF/700</t>
+  </si>
+  <si>
+    <t>WAB9650011030 AV</t>
   </si>
   <si>
     <t>DANA</t>
   </si>
   <si>
+    <t>FRAS-LE</t>
+  </si>
+  <si>
     <t>WABCO</t>
   </si>
   <si>
     <t>KIT SPLINDER AGRALE 170MM x 33MM</t>
   </si>
   <si>
-    <t>PEDAL CLUTCH M2-106  M2-112 COLUMBIA CARRERA O DESPLAZAMIENTO 194 MM</t>
+    <t>BLOQUE TRASERA Y TRAILER (1 JG VIENE X 8 BLOQUES) PARA MACK  R600 -R700/CHEVOLET SUPER BRIGARDIER, KODIAK/ BRIGADIER / DODGE 600 f /INTERNATIONAL 4300-HI-HI500 / FORD F800,FT9000 FREIGHTLINER/MACK/ROMARCO TRAILER  (solo si la zapata tiene 7 pulgadas de ancho)/DITE TRAILER/INCA FRUEHAUE TRAILER</t>
+  </si>
+  <si>
+    <t>BLOQUE TRASERA Y TRAILER PARA (1 JG VIENE X 8 BLOQUES) PARA MACK  R600 -R700/CHEVOLET SUPER BRIGARDIER, KODIAK/ BRIGADIER / DODGE 600 f /INTERNATIONAL 4300-HI-HI500 / FORD F800,FT9000 FREIGHTLINER/MACK/ROMARCO TRAILER (solo si la zapata tiene 7 pulgadas de ancho)/DITE TRAILER/INCA FRUEHAUE TRAILER</t>
+  </si>
+  <si>
+    <t>BLOQUE TRASERO  (1 JG VIENE X 8 BLOQUES) PARA KENWORTH T300-T800/MACK CT713INTERNATIONAL 4700 -4300-7600/ ROCKWELL AXLE / FREIGHTLINER M2 106-112</t>
+  </si>
+  <si>
+    <t>BLOQUE TRASERA (1 JG VIENE X 8 BLOQUES) PARA KENWORTH T300-T800/MACK CT713INTERNATIONAL 4700 -4300-7600/ ROCKWELL AXLE / FREIGHTLINER M2 106-112</t>
+  </si>
+  <si>
+    <t>BLOQUE TRASERA (1 JG VIENE X 8 BLOQUES) PARA INTERNATIONAL 9400--9900/EATON BRAKES 16.5" DIA. X 7" /MERCEDES CAMION CLASE7 / KENWORTH T600,T800 EJE EATON MODELO 2002-2007-CAMION 7600 INTER</t>
+  </si>
+  <si>
+    <t>BLOQUE DELANTERO (1 JG VIENE X 8 BLOQUES) PARA FREIGHTLINER  COLUMBIA-M2 106 -112 -CASCADIA/INTERNATIONAL  7600-4300-PROSTAR/ KENWORTH T800, MERITOR TAMBOR DIA 16,5" X ANCHO 5"/ COMPAÑERO CON EL 4707</t>
+  </si>
+  <si>
+    <t>BLOQUE DELANTERO PARA KENWORTH MINIMULA- T300-T800 MODELO NUEVO, TANDEM EATON / EJE EATON AXLE DIA. 16.5” X ANCHO. 5"/INTERNATIONAL HI 4300- HI 7400-9400 TRACTO CAMION /1 JUEGO VIENE X 8 BLOQUES</t>
+  </si>
+  <si>
+    <t>BLOQUE DELANTERO (1 JG VIENE X 8 BLOQUES) PARA FORD F-800/INTERNATIONAL 4700, 9400 TAMBOR DIA 16.5" X 6 " ANCHO /EJE ROCKWELL./BLUE BIRD./FRENO DELANTERO BOLQUETA INTERNATIONAL 7600</t>
+  </si>
+  <si>
+    <t>BLOQUE TRASERO PARA FORD CARGO 1721/AGRALE 1721/IVECO EURO CARGO TECTOR 170E22/EJE ROCKWELL 15"X6"/VW CAMION 2004-2012 -vw Costelllation/ FORD CARGO volkswagen/1 JUEGO VIENE X 8 BLOQUES</t>
+  </si>
+  <si>
+    <t>BLOQUE TRASERA CON SOBRE MEDIDA PARA INTERNATIONAL 9400--9900/EATON BRAKES 16.5" DIA. X 7" /MERCEDES CAMION CLASE7 / KENWORTH T600,T800 EJE EATON MODELO 2002-2007-CAMION 7600 INTER./1 JUEGO TIENE 8 BLOQUES; (KENWORTH T800 PARA EJE MARCA DANA) VENTA MINIMA 1 CAJA QUE TRAE 2 JUEGOS (16 BLOQUES) EL PRECIO DE LISTA ES POR 1 JUEGO</t>
+  </si>
+  <si>
+    <t>BLOQUE TRASERA ESTANDAR (COMPAÑERO DEL 4719)PARA INTERNATIONAL 9400--9900/EATON BRAKES 16.5" DIA. X 7" /MERCEDES CAMION CLASE7 / KENWORTH T600,T800 EJE EATON MODELO 2002-2007-CAMION 7600 INTER</t>
+  </si>
+  <si>
+    <t>BLOQUE PARA TRAILER (CON SOBRE MEDIDA .86 MILESIMAS DE PULGADA MAS GRUESO) PARA TRAILER RANDON CAMPANA 16.5" DIA, X8"  Y TRASERO DAF CF 530/</t>
+  </si>
+  <si>
+    <t>BLOQUE DELANTERO ESTANDAR (COMPAÑERO DEL 4709) PARA KENWORTH MINIMULA- T300-T800 MODELO NUEVO, TANDEM EATON / EJE EATON AXLE DIA. 16.5” X ANCHO. 5"/INTERNATIONAL HI 4300- HI 7400-9400 TRACTO CAMION( KENWORTH T800 PARA EJE MARCA DANA)</t>
+  </si>
+  <si>
+    <t>BLOQUE TRASERO ESTANDAR ARTICULADO MERCEDES BENZ OH 400 SHACMAN CAMION</t>
+  </si>
+  <si>
+    <t>BLOQUE TRASERO (CON SOBRE MEDIDA .86 MILESIMAS DE PULGADA MAS GRUESO) ARTICULADO MERCEDES BENZ OH 400 SHACMAN CAMION</t>
+  </si>
+  <si>
+    <t>PEDAL CLUTCH M2-106 M2-112 COLUMBIA CARRERA O DESPLAZAMIENTO 194 MM</t>
   </si>
   <si>
     <t>Unidad</t>
@@ -94,13 +190,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 30/11/2025 08:47:22</t>
+    <t>Período: 31/12/2025 08:45:38</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 26/11/2025 08:48:16</t>
+    <t>Fecha y hora de generación: 04/12/2025 08:46:34</t>
   </si>
 </sst>
 </file>
@@ -514,28 +610,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -551,7 +647,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="3" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -567,12 +663,12 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="4" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="I7" s="5" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -624,19 +720,19 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I10" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -650,34 +746,546 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
       </c>
       <c r="C11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I11" t="s">
+        <v>52</v>
+      </c>
+      <c r="J11">
+        <v>150</v>
+      </c>
+      <c r="K11">
+        <v>102620.39</v>
+      </c>
+      <c r="L11">
+        <v>15393058.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" t="s">
+        <v>33</v>
+      </c>
+      <c r="I12" t="s">
+        <v>52</v>
+      </c>
+      <c r="J12">
+        <v>160</v>
+      </c>
+      <c r="K12">
+        <v>99787.28999999999</v>
+      </c>
+      <c r="L12">
+        <v>15965966.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="D11" t="s">
+      <c r="C13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" t="s">
+        <v>33</v>
+      </c>
+      <c r="I13" t="s">
+        <v>52</v>
+      </c>
+      <c r="J13">
+        <v>150</v>
+      </c>
+      <c r="K13">
+        <v>116667.33</v>
+      </c>
+      <c r="L13">
+        <v>17500099.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" t="s">
+        <v>33</v>
+      </c>
+      <c r="I14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J14">
+        <v>270</v>
+      </c>
+      <c r="K14">
+        <v>110881.06</v>
+      </c>
+      <c r="L14">
+        <v>29937886.2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
         <v>19</v>
       </c>
-      <c r="E11" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" t="s">
-        <v>17</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="C15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" t="s">
+        <v>33</v>
+      </c>
+      <c r="I15" t="s">
+        <v>52</v>
+      </c>
+      <c r="J15">
+        <v>90</v>
+      </c>
+      <c r="K15">
+        <v>121355.41</v>
+      </c>
+      <c r="L15">
+        <v>10921986.9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
         <v>20</v>
       </c>
-      <c r="J11">
-        <v>57</v>
-      </c>
-      <c r="K11">
+      <c r="C16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" t="s">
+        <v>33</v>
+      </c>
+      <c r="I16" t="s">
+        <v>52</v>
+      </c>
+      <c r="J16">
+        <v>60</v>
+      </c>
+      <c r="K16">
+        <v>113448.51</v>
+      </c>
+      <c r="L16">
+        <v>6806910.6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" t="s">
+        <v>33</v>
+      </c>
+      <c r="I17" t="s">
+        <v>52</v>
+      </c>
+      <c r="J17">
+        <v>20</v>
+      </c>
+      <c r="K17">
+        <v>80383.44</v>
+      </c>
+      <c r="L17">
+        <v>1607668.8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" t="s">
+        <v>33</v>
+      </c>
+      <c r="I18" t="s">
+        <v>52</v>
+      </c>
+      <c r="J18">
+        <v>20</v>
+      </c>
+      <c r="K18">
+        <v>86647.49000000001</v>
+      </c>
+      <c r="L18">
+        <v>1732949.8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" t="s">
+        <v>33</v>
+      </c>
+      <c r="I19" t="s">
+        <v>52</v>
+      </c>
+      <c r="J19">
+        <v>45</v>
+      </c>
+      <c r="K19">
+        <v>96033.96000000001</v>
+      </c>
+      <c r="L19">
+        <v>4321528.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20" t="s">
+        <v>33</v>
+      </c>
+      <c r="I20" t="s">
+        <v>52</v>
+      </c>
+      <c r="J20">
+        <v>5</v>
+      </c>
+      <c r="K20">
+        <v>108467.5</v>
+      </c>
+      <c r="L20">
+        <v>542337.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" t="s">
+        <v>33</v>
+      </c>
+      <c r="F21" t="s">
+        <v>33</v>
+      </c>
+      <c r="I21" t="s">
+        <v>52</v>
+      </c>
+      <c r="J21">
+        <v>5</v>
+      </c>
+      <c r="K21">
+        <v>156752</v>
+      </c>
+      <c r="L21">
+        <v>783760</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" t="s">
+        <v>33</v>
+      </c>
+      <c r="I22" t="s">
+        <v>52</v>
+      </c>
+      <c r="J22">
+        <v>20</v>
+      </c>
+      <c r="K22">
+        <v>149507.25</v>
+      </c>
+      <c r="L22">
+        <v>2990145</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E23" t="s">
+        <v>33</v>
+      </c>
+      <c r="F23" t="s">
+        <v>33</v>
+      </c>
+      <c r="I23" t="s">
+        <v>52</v>
+      </c>
+      <c r="J23">
+        <v>5</v>
+      </c>
+      <c r="K23">
+        <v>120840</v>
+      </c>
+      <c r="L23">
+        <v>604200</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" t="s">
+        <v>48</v>
+      </c>
+      <c r="E24" t="s">
+        <v>33</v>
+      </c>
+      <c r="F24" t="s">
+        <v>33</v>
+      </c>
+      <c r="I24" t="s">
+        <v>52</v>
+      </c>
+      <c r="J24">
+        <v>5</v>
+      </c>
+      <c r="K24">
+        <v>120172</v>
+      </c>
+      <c r="L24">
+        <v>600860</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" t="s">
+        <v>49</v>
+      </c>
+      <c r="E25" t="s">
+        <v>33</v>
+      </c>
+      <c r="F25" t="s">
+        <v>33</v>
+      </c>
+      <c r="I25" t="s">
+        <v>52</v>
+      </c>
+      <c r="J25">
+        <v>20</v>
+      </c>
+      <c r="K25">
+        <v>114126</v>
+      </c>
+      <c r="L25">
+        <v>2282520</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" t="s">
+        <v>50</v>
+      </c>
+      <c r="E26" t="s">
+        <v>33</v>
+      </c>
+      <c r="F26" t="s">
+        <v>33</v>
+      </c>
+      <c r="I26" t="s">
+        <v>52</v>
+      </c>
+      <c r="J26">
+        <v>10</v>
+      </c>
+      <c r="K26">
+        <v>122062</v>
+      </c>
+      <c r="L26">
+        <v>1220620</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" t="s">
+        <v>51</v>
+      </c>
+      <c r="E27" t="s">
+        <v>34</v>
+      </c>
+      <c r="F27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I27" t="s">
+        <v>52</v>
+      </c>
+      <c r="J27">
+        <v>56</v>
+      </c>
+      <c r="K27">
         <v>1268236.6</v>
       </c>
-      <c r="L11">
-        <v>72289486.2</v>
+      <c r="L27">
+        <v>71021249.59999999</v>
       </c>
     </row>
   </sheetData>

--- a/VALORIZADO TOBERIN.xlsx
+++ b/VALORIZADO TOBERIN.xlsx
@@ -82,13 +82,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 31/01/2026 07:41:41</t>
+    <t>Período: 31/01/2026 07:41:40</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 08/01/2026 07:42:14</t>
+    <t>Fecha y hora de generación: 09/01/2026 07:42:12</t>
   </si>
 </sst>
 </file>

--- a/VALORIZADO TOBERIN.xlsx
+++ b/VALORIZADO TOBERIN.xlsx
@@ -82,13 +82,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 31/01/2026 07:41:40</t>
+    <t>Período: 31/01/2026 08:56:04</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 09/01/2026 07:42:12</t>
+    <t>Fecha y hora de generación: 19/01/2026 08:56:17</t>
   </si>
 </sst>
 </file>
